--- a/xlsx/Deep Supervised Point Cloud Registration Literature (2021-2024).xlsx
+++ b/xlsx/Deep Supervised Point Cloud Registration Literature (2021-2024).xlsx
@@ -2,8 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13,16 +17,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -31,25 +31,28 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -122,56 +125,114 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -183,626 +244,649 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>年份</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>算法/论文简称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>引用次数</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>完整学术引用格式</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>ReAgent</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" t="n">
         <v>76</v>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Bauer, D., Patten, T., &amp; Vincze, M. (2021). Reagent: Point cloud registration using imitation and reinforcement learning. In: IEEE Conference on Computer Vision and Pattern Recognition, pp 14586–14594.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr"/>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>PointNetLK Revisited</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" t="n">
         <v>109</v>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Li, X., Pontes, J. K., &amp; Lucey, S. (2021). Pointnetlk revisited. In: IEEE Conference on Computer Vision and Pattern Recognition, pp 12763–12772.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>PCR-CG</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" t="n">
         <v>49</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Zhang, Y., Yu, J., Huang, X., Zhou, W., &amp; Hou, J. (2022). Pcr-cg: Point cloud registration via deep explicit color and geometry. In: European Conference on Computer Vision, Springer, pp 443–459.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
         <is>
           <t>IMFNET</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" t="n">
         <v>77</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Huang, X., Qu, W., Zuo, Y., Fang, Y., &amp; Zhao, X. (2022). Imfnet: Interpretable multimodal fusion for point cloud registration. IEEE Robotics and Automation Letters, 7(4), 12323–12330.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
         <is>
           <t>ImLoveNet</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Chen, H., Wei, Z., Xu, Y., Wei, M., &amp; Wang, J. (2022). Imlovenet: Misaligned image-supported registration network for low-overlap point cloud pairs. In: ACM Special Interest Group on Computer Graphics and Interactive Techniques, pp 1–9.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
         <is>
           <t>GMF</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Huang, X., Qu, W., Zuo, Y., Fang, Y., &amp; Zhao, X. (2022). Gmf: General multimodal fusion framework for correspondence outlier rejection. IEEE Robotics and Automation Letters, 7(4), 12585–12592.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
         <is>
           <t>SCRnet</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" t="n">
         <v>9</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Shao, H., Zhang, Z., Feng, X., &amp; Zeng, D. (2022). Scrnet: A spatial consistency guided network using contrastive learning for point cloud registration. Symmetry, 14(1), 140.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr"/>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
         <is>
           <t>DCPCR</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" t="n">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Wiesmann, L., Guadagnino, T., Vizzo, I., Grisetti, G., Behley, J., &amp; Stachniss, C. (2022). Dcpcr: Deep compressed point cloud registration in large-scale outdoor environments. IEEE Robotics and Automation Letters, 7(3), 6327–6334.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr"/>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Global-PBNet</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" t="n">
         <v>157</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Zheng, Y., Li, Y., Yang, S., &amp; Lu, H. (2022). Global-pbnet: A novel point cloud registration for autonomous driving. IEEE Transactions on Intelligent Transportation Systems, 23(11), 22312–22319.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="A11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>OGMM</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" t="n">
         <v>60</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Mei, G., Poiesi, F., Saltori, C., Zhang, J., Ricci, E., &amp; Sebe, N. (2023). Overlap-guided gaussian mixture models for point cloud registration. In: IEEE/CVF Winter Conference on Applications of Computer Vision, pp 4511–4520.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr"/>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Chen et al. (GMM)</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Chen, H., Chen, B., Zhao, Z., &amp; Song, B. (2023). Point cloud registration based on learning gaussian mixture models with global-weighted local representations. IEEE Geoscience and Remote Sensing Letters, 20, 1–5.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr"/>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
         <is>
           <t>VBReg</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" t="n">
         <v>86</v>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Jiang, H., Dang, Z., Wei, Z., Xie, J., Yang, J., &amp; Salzmann, M. (2023). Robust outlier rejection for 3d registration with variational bayes. In: IEEE Conference on Computer Vision and Pattern Recognition, pp 1148–1157.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr"/>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Regiffusion</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Xu, J., Zhang, Y., Zou, Y., Liu, P. X. (2023). Point cloud registration with zero overlap rate and negative overlap rate. IEEE Robotics and Automation Letters.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr"/>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
         <is>
           <t>DiffusionPCR</t>
         </is>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Chen, Z., Ren, Y., Zhang, T., Dang, Z., Tao, W., Süsstrunk, S., &amp; Salzmann, M. (2023). Diffusionpcr: Diffusion models for robust multi-step point cloud registration. arXiv preprint, arXiv:2312.03053.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
         <is>
           <t>SIRA-PCR</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" t="n">
         <v>47</v>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Chen, S., Xu, H., Li, R., Liu, G., Fu, C. W., &amp; Liu, S. (2023). Sira-pcr: Sim-to-real adaptation for 3d point cloud registration. In: IEEE Conference on Computer Vision and Pattern Recognition, pp 14394–14405.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr"/>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Yuan et al.</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" t="n">
         <v>23</v>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Yuan, M., Huang, X., Fu, K., Li, Z., &amp; Wang, M. (2023). Boosting 3D point cloud registration by transferring multi-modality knowledge. In: IEEE International Conference on Robotics and Automation, IEEE, pp 11734–11741.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
         <is>
           <t>ZeroReg</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Wang, W., Mei, G., Ren, B., Huang, X., Poiesi, F., Van Gool, L., Sebe, N., &amp; Lepri, B. (2023). Zero-shot point cloud registration. arXiv preprint, arXiv:2312.03032.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Liu et al.</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" t="n">
         <v>31</v>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Liu, Q., Zhu, H., Zhou, Y., Li, H., Chang, S., &amp; Guo, M. (2023). Density-invariant features for distant point cloud registration. In: IEEE International Conference on Computer Vision, pp 18215–18225.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Point-TTA</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" t="n">
         <v>32</v>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Hatem, A., Qian, Y., &amp; Wang, Y. (2023). Point-tta: Test-time adaptation for point cloud registration using multitask meta-auxiliary learning. In: IEEE International Conference on Computer Vision, pp 16494–16504.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Chen et al. (RL)</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Chen, B. (2023). Point cloud registration via heuristic reward reinforcement learning. Stats, 6(1), 268–278.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="A22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>PosDiffNet</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>She, R., Wang, S., Kang, Q., Zhao, K., Song, Y., Tay, W. P., Geng, T., &amp; Jian, X. (2024). PosDiffNet: Positional Neural Diffusion for Point Cloud Registration in a Large Field of View with Perturbations. AAAI Conference on Artificial Intelligence, 38, 231–239.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
         <is>
           <t>PointDifformer</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" t="n">
         <v>40</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>She, R., Kang, Q., Wang, S., Tay, W. P., Zhao, K., Song, Y., Geng, T., Xu, Y., Navarro, D. N., &amp; Hartmannsgruber, A. (2024). Point-difformer: Robust point cloud registration with neural diffusion and transformer. IEEE Transactions on Geoscience and Remote Sensing.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr"/>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Jiang et al.</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" t="n">
         <v>70</v>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Jiang, H., Salzmann, M., Dang, Z., Xie, J., &amp; Yang, J. (2024). Se (3) diffusion model-based point cloud registration for robust 6d object pose estimation. Advances in Neural Information Processing Systems 36.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Diff-Reg</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" t="n">
         <v>27</v>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Wu, Q., Jiang, H., Luo, L., Li, J., Ding, Y., Xie, J., &amp; Yang, J. (2024). Diff-reg: diffusion model in doubly stochastic matrix space for registration problem. In: European Conference on Computer Vision, Springer, pp 160–178.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>IGReg</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" t="n">
         <v>17</v>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Xu, Z., Jiang, X., Gao, X., Gao, R., Gu, C., Zhang, Q., Li, W., &amp; Gao, X. (2024). Igreg: Image-geometry-assisted point cloud registration via selective correlation fusion. IEEE Transactions on Multimedia, 26, 7475–7489.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
         <is>
           <t>SemReg</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" t="n">
         <v>13</v>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Fung, S., Lu, X., Edirimuni, D. d. S., Pan, W., Liu, X., &amp; Li, H. (2024). Semreg: Semantics constrained point cloud registration. In: European Conference on Computer Vision, Springer, pp 293–310.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
         <is>
           <t>PointRegGPT</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" t="n">
         <v>7</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Chen, S., Xu, H., Li, H., Luo, K., Liu, G., Fu, C. W., Tan, P., &amp; Liu, S. (2024). Pointreggpt: Boosting 3d point cloud registration using generative point-cloud pairs for training. European Conference on Computer Vision pp 272–289.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr"/>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
         <is>
           <t>UMERegRobust</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr"/>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Haitman, Y., Efraim, A., &amp; Francos, J. M. (2024). Uneregrobust-universal manifold embedding compatible features for robust point cloud registration. In: European Conference on Computer Vision, Springer, pp 358–374.</t>
         </is>
